--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbc9f0bb248b3f74/Bureau/siteanais/Portfolio/t_competences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{34F75D9C-4FAB-4279-B9B4-691CBE1EE43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7003BAC7-ED3C-4028-8352-930453307BBC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D272D328-B155-44A2-9186-A6E0C3A4D178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -230,6 +230,15 @@
   </si>
   <si>
     <t>▸Mettre en œuvre des outils et des stratégies de veille informationnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet Android </t>
+  </si>
+  <si>
+    <t>03/11/2025 au 15/12/2025</t>
+  </si>
+  <si>
+    <t>▸Analyser les objectifs et les modalités d’organisation d’un projet</t>
   </si>
 </sst>
 </file>
@@ -363,7 +372,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -653,6 +662,58 @@
       </right>
       <top style="thin">
         <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -665,7 +726,7 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -767,6 +828,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -776,29 +861,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1191,7 +1285,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.109375" style="1" customWidth="1"/>
@@ -1208,56 +1302,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
@@ -1269,22 +1363,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1307,8 +1401,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="8" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
@@ -1329,14 +1423,14 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:13" s="8" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
@@ -1431,91 +1525,97 @@
       <c r="B14" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="20"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23" t="s">
+      <c r="E14" s="49"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="H14" s="51"/>
+    </row>
+    <row r="15" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="53"/>
+      <c r="H15" s="55"/>
+    </row>
+    <row r="16" spans="1:13" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+    </row>
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B17" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23" t="s">
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="22" t="s">
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I17" s="28" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A18" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-    </row>
-    <row r="18" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B19" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="23" t="s">
+      <c r="C19" s="11"/>
+      <c r="D19" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
@@ -1525,7 +1625,7 @@
       <c r="G20" s="11"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="10"/>
       <c r="C21" s="11"/>
@@ -1535,7 +1635,7 @@
       <c r="G21" s="11"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
@@ -1545,7 +1645,7 @@
       <c r="G22" s="11"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
@@ -1555,40 +1655,50 @@
       <c r="G23" s="11"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-    </row>
-    <row r="25" spans="1:8" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
+    <row r="24" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="16"/>
+    </row>
+    <row r="25" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbc9f0bb248b3f74/Bureau/siteanais/Portfolio/t_competences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D272D328-B155-44A2-9186-A6E0C3A4D178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEFA4962-8670-4CA2-B6D0-37DB6851958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$20</definedName>
   </definedNames>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
@@ -28,12 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2024</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -114,9 +111,6 @@
     <t>NOM et prénom : PORTOLLEAU Anaïs</t>
   </si>
   <si>
-    <t>Centre de formation : Joliverie</t>
-  </si>
-  <si>
     <t xml:space="preserve">08/01/2024 au 12/01/2024 </t>
   </si>
   <si>
@@ -130,9 +124,6 @@
   </si>
   <si>
     <t>13/05/2024 au 21/06/2024</t>
-  </si>
-  <si>
-    <t>Stage - 1ère année SIO à Orcab Artisans Artipole                                                  Application pour vérifier les urls/liens saisies par les coopératives dans DataSiteOrcab</t>
   </si>
   <si>
     <t xml:space="preserve">▸Collecter, suivre et orienter des demandes </t>
@@ -184,9 +175,6 @@
     <t>▸Participer à l’évolution d’un site Web exploitant les données de l’organisation.</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/</t>
-  </si>
-  <si>
     <t>Projet Web - Intranet</t>
   </si>
   <si>
@@ -223,9 +211,6 @@
     <t>▸Mettre en place son environnement d’apprentissage personnel                                                                                                                                                ▸Gérer son identité professionnelle</t>
   </si>
   <si>
-    <t>Stage - 2nd année de BTS SIO à Delia Technologies - Applicationpour gérer</t>
-  </si>
-  <si>
     <t>05/01/26 au 12/02/26</t>
   </si>
   <si>
@@ -239,6 +224,38 @@
   </si>
   <si>
     <t>▸Analyser les objectifs et les modalités d’organisation d’un projet</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Centre de formation : La Joliverie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pennylane </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage - 2nd année de BTS SIO à Delia Technologies - Application web pour gérer les factures/transactions </t>
+  </si>
+  <si>
+    <t>Stage - 1ère année SIO à Orcab Artisans Artipole - Application pour vérifier les urls/liens saisies par les coopératives dans DataSiteOrcab</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adresse URL du portfolio :  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://anaisprt44.github.io/Portfolio/</t>
+    </r>
+  </si>
+  <si>
+    <t>▸Déployer un service</t>
   </si>
 </sst>
 </file>
@@ -372,7 +389,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -604,51 +621,6 @@
         <color rgb="FF4A452A"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FF4A452A"/>
       </bottom>
       <diagonal/>
@@ -726,7 +698,7 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -752,18 +724,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -773,18 +736,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -802,9 +753,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -825,15 +773,54 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -852,47 +839,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1285,7 +1239,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.109375" style="1" customWidth="1"/>
@@ -1302,396 +1256,336 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="37"/>
+    </row>
+    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="43"/>
-    </row>
-    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+    </row>
+    <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-    </row>
-    <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+    </row>
+    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="8" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="47"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+    </row>
+    <row r="9" spans="1:13" s="8" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:13" s="8" customFormat="1" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="2" t="s">
+      <c r="C10" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:13" s="8" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="G12" s="13"/>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:13" s="8" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-    </row>
-    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="8" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="31"/>
+    </row>
+    <row r="15" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="33"/>
+      <c r="H15" s="35"/>
+    </row>
+    <row r="16" spans="1:13" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-    </row>
-    <row r="9" spans="1:13" s="8" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+    </row>
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="22"/>
-    </row>
-    <row r="10" spans="1:13" s="8" customFormat="1" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" spans="1:13" s="8" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="22"/>
-    </row>
-    <row r="12" spans="1:13" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21"/>
-    </row>
-    <row r="13" spans="1:13" s="8" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+    </row>
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A18" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50" t="s">
+      <c r="C19" s="9"/>
+      <c r="D19" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="51"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
+      <c r="I19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="53"/>
-      <c r="H15" s="55"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-    </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="16"/>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
-    </row>
-    <row r="26" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+    </row>
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:E4"/>
@@ -1699,6 +1593,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbc9f0bb248b3f74/Bureau/siteanais/Portfolio/t_competences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEFA4962-8670-4CA2-B6D0-37DB6851958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{CEFA4962-8670-4CA2-B6D0-37DB6851958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23043BE9-0DDE-4C93-842E-8DB0E00FAE6F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -241,9 +241,18 @@
     <t>Stage - 1ère année SIO à Orcab Artisans Artipole - Application pour vérifier les urls/liens saisies par les coopératives dans DataSiteOrcab</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Adresse URL du portfolio :  </t>
-    </r>
+    <t>▸Déployer un service</t>
+  </si>
+  <si>
+    <t>09/03/2026 au 30/03/2026</t>
+  </si>
+  <si>
+    <t>Projet Java - Application de modération du site R3st0.fr</t>
+  </si>
+  <si>
+    <t>Déployer un service</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -251,11 +260,19 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">Adresse URL du portfolio :  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color theme="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>https://anaisprt44.github.io/Portfolio/</t>
     </r>
-  </si>
-  <si>
-    <t>▸Déployer un service</t>
   </si>
 </sst>
 </file>
@@ -265,7 +282,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* \-??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -321,12 +338,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -347,12 +358,6 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -368,14 +373,41 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <u/>
-      <sz val="10"/>
+      <sz val="18"/>
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -695,10 +727,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -724,87 +756,102 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -815,21 +862,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -839,14 +883,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1239,7 +1277,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ20"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.109375" style="1" customWidth="1"/>
@@ -1256,83 +1294,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="37"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
       <c r="F4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
+      <c r="A5" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="50" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1355,8 +1393,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="8" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
@@ -1377,217 +1415,245 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:13" s="8" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="1:13" s="8" customFormat="1" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="1:13" s="8" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="1:13" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="32"/>
     </row>
     <row r="13" spans="1:13" s="8" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13" t="s">
+      <c r="B13" s="34"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="32"/>
+    </row>
+    <row r="14" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="24"/>
+      <c r="I14" s="32"/>
+    </row>
+    <row r="15" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="32"/>
+    </row>
+    <row r="16" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="25" t="s">
+      <c r="C16" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="28"/>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="32"/>
+    </row>
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="32"/>
+    </row>
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="35"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-    </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="15" t="s">
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I20" s="32" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
+    <row r="21" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
@@ -1599,8 +1665,11 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A5:H5" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbc9f0bb248b3f74/Bureau/siteanais/Portfolio/t_competences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{CEFA4962-8670-4CA2-B6D0-37DB6851958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23043BE9-0DDE-4C93-842E-8DB0E00FAE6F}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{CEFA4962-8670-4CA2-B6D0-37DB6851958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFED694E-B9CC-4C55-8E14-87B82C40FEF1}"/>
   <bookViews>
-    <workbookView xWindow="-14775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$B$2:$I$21</definedName>
   </definedNames>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
@@ -144,28 +144,6 @@
     <t xml:space="preserve">Option : </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <strike/>
-        <sz val="18"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>▢</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> SLAM</t>
-    </r>
-  </si>
-  <si>
     <t>Projet AP Web - Bibliothèque associative</t>
   </si>
   <si>
@@ -203,9 +181,6 @@
   </si>
   <si>
     <t>▸Accompagner les utilisateurs dans la mise en place d’un service  ▸Déployer un service</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Mettre en œuvre des outils et stratégies de veille informationnelle                                            </t>
   </si>
   <si>
     <t>▸Mettre en place son environnement d’apprentissage personnel                                                                                                                                                ▸Gérer son identité professionnelle</t>
@@ -274,6 +249,30 @@
       <t>https://anaisprt44.github.io/Portfolio/</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="18"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>▢</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SLAM</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">▸Mettre en œuvre des outils et stratégies de veille informationnelle                                            </t>
+  </si>
 </sst>
 </file>
 
@@ -282,39 +281,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* \-??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -324,40 +294,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -387,28 +326,44 @@
     </font>
     <font>
       <b/>
+      <u/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <i/>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="18"/>
-      <color theme="10"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -421,7 +376,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -430,21 +385,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF4A452A"/>
       </left>
@@ -511,21 +451,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
-    </border>
     <border diagonalDown="1">
       <left style="medium">
         <color rgb="FF4A452A"/>
@@ -540,21 +465,6 @@
       <diagonal style="thin">
         <color rgb="FF4A452A"/>
       </diagonal>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -595,21 +505,6 @@
         <color rgb="FF4A452A"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF4A452A"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -724,167 +619,370 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalDown="1">
+      <left style="medium">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal style="thin">
+        <color rgb="FF4A452A"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A452A"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF4A452A"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4A452A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF4A452A"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1277,399 +1375,1834 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ21"/>
+  <dimension ref="A1:AWV32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="75.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="41.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="33.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="39.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" customWidth="1"/>
-    <col min="10" max="43" width="11.44140625" customWidth="1"/>
-    <col min="44" max="16384" width="10.88671875" style="1"/>
+    <col min="1" max="1" width="10.88671875" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="75.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="41.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="2:1296" x14ac:dyDescent="0.25">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="2:1296" ht="31.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="6"/>
+      <c r="BG2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="6"/>
+      <c r="BJ2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="6"/>
+      <c r="BT2" s="6"/>
+      <c r="BU2" s="6"/>
+      <c r="BV2" s="6"/>
+      <c r="BW2" s="6"/>
+      <c r="BX2" s="6"/>
+      <c r="BY2" s="6"/>
+      <c r="BZ2" s="6"/>
+      <c r="CA2" s="6"/>
+      <c r="CB2" s="6"/>
+      <c r="CC2" s="6"/>
+      <c r="CD2" s="6"/>
+      <c r="CE2" s="6"/>
+      <c r="CF2" s="6"/>
+      <c r="CG2" s="6"/>
+      <c r="CH2" s="6"/>
+      <c r="CI2" s="6"/>
+      <c r="CJ2" s="6"/>
+      <c r="CK2" s="6"/>
+      <c r="CL2" s="6"/>
+      <c r="CM2" s="6"/>
+      <c r="CN2" s="6"/>
+      <c r="CO2" s="6"/>
+      <c r="CP2" s="6"/>
+      <c r="CQ2" s="6"/>
+      <c r="CR2" s="6"/>
+      <c r="CS2" s="6"/>
+      <c r="CT2" s="6"/>
+      <c r="CU2" s="6"/>
+      <c r="CV2" s="6"/>
+      <c r="CW2" s="6"/>
+      <c r="CX2" s="6"/>
+      <c r="CY2" s="6"/>
+      <c r="CZ2" s="6"/>
+      <c r="DA2" s="6"/>
+      <c r="DB2" s="6"/>
+      <c r="DC2" s="6"/>
+      <c r="DD2" s="6"/>
+      <c r="DE2" s="6"/>
+      <c r="DF2" s="6"/>
+      <c r="DG2" s="6"/>
+      <c r="DH2" s="6"/>
+      <c r="DI2" s="6"/>
+      <c r="DJ2" s="6"/>
+      <c r="DK2" s="6"/>
+      <c r="DL2" s="6"/>
+      <c r="DM2" s="6"/>
+      <c r="DN2" s="6"/>
+      <c r="DO2" s="6"/>
+      <c r="DP2" s="6"/>
+      <c r="DQ2" s="6"/>
+      <c r="DR2" s="6"/>
+      <c r="DS2" s="6"/>
+      <c r="DT2" s="6"/>
+      <c r="DU2" s="6"/>
+      <c r="DV2" s="6"/>
+      <c r="DW2" s="6"/>
+      <c r="DX2" s="6"/>
+      <c r="DY2" s="6"/>
+      <c r="DZ2" s="6"/>
+      <c r="EA2" s="6"/>
+      <c r="EB2" s="6"/>
+      <c r="EC2" s="6"/>
+      <c r="ED2" s="6"/>
+      <c r="EE2" s="6"/>
+      <c r="EF2" s="6"/>
+      <c r="EG2" s="6"/>
+      <c r="EH2" s="6"/>
+      <c r="EI2" s="6"/>
+      <c r="EJ2" s="6"/>
+      <c r="EK2" s="6"/>
+      <c r="EL2" s="6"/>
+      <c r="EM2" s="6"/>
+      <c r="EN2" s="6"/>
+      <c r="EO2" s="6"/>
+      <c r="EP2" s="6"/>
+      <c r="EQ2" s="6"/>
+      <c r="ER2" s="6"/>
+      <c r="ES2" s="6"/>
+      <c r="ET2" s="6"/>
+      <c r="EU2" s="6"/>
+      <c r="EV2" s="6"/>
+      <c r="EW2" s="6"/>
+      <c r="EX2" s="6"/>
+      <c r="EY2" s="6"/>
+      <c r="EZ2" s="6"/>
+      <c r="FA2" s="6"/>
+      <c r="FB2" s="6"/>
+      <c r="FC2" s="6"/>
+      <c r="FD2" s="6"/>
+      <c r="FE2" s="6"/>
+      <c r="FF2" s="6"/>
+      <c r="FG2" s="6"/>
+      <c r="FH2" s="6"/>
+      <c r="FI2" s="6"/>
+      <c r="FJ2" s="6"/>
+      <c r="FK2" s="6"/>
+      <c r="FL2" s="6"/>
+      <c r="FM2" s="6"/>
+      <c r="FN2" s="6"/>
+      <c r="FO2" s="6"/>
+      <c r="FP2" s="6"/>
+      <c r="FQ2" s="6"/>
+      <c r="FR2" s="6"/>
+      <c r="FS2" s="6"/>
+      <c r="FT2" s="6"/>
+      <c r="FU2" s="6"/>
+      <c r="FV2" s="6"/>
+      <c r="FW2" s="6"/>
+      <c r="FX2" s="6"/>
+      <c r="FY2" s="6"/>
+      <c r="FZ2" s="6"/>
+      <c r="GA2" s="6"/>
+      <c r="GB2" s="6"/>
+      <c r="GC2" s="6"/>
+      <c r="GD2" s="6"/>
+      <c r="GE2" s="6"/>
+      <c r="GF2" s="6"/>
+      <c r="GG2" s="6"/>
+      <c r="GH2" s="6"/>
+      <c r="GI2" s="6"/>
+      <c r="GJ2" s="6"/>
+      <c r="GK2" s="6"/>
+      <c r="GL2" s="6"/>
+      <c r="GM2" s="6"/>
+      <c r="GN2" s="6"/>
+      <c r="GO2" s="6"/>
+      <c r="GP2" s="6"/>
+      <c r="GQ2" s="6"/>
+      <c r="GR2" s="6"/>
+      <c r="GS2" s="6"/>
+      <c r="GT2" s="6"/>
+      <c r="GU2" s="6"/>
+      <c r="GV2" s="6"/>
+      <c r="GW2" s="6"/>
+      <c r="GX2" s="6"/>
+      <c r="GY2" s="6"/>
+      <c r="GZ2" s="6"/>
+      <c r="HA2" s="6"/>
+      <c r="HB2" s="6"/>
+      <c r="HC2" s="6"/>
+      <c r="HD2" s="6"/>
+      <c r="HE2" s="6"/>
+      <c r="HF2" s="6"/>
+      <c r="HG2" s="6"/>
+      <c r="HH2" s="6"/>
+      <c r="HI2" s="6"/>
+      <c r="HJ2" s="6"/>
+      <c r="HK2" s="6"/>
+      <c r="HL2" s="6"/>
+      <c r="HM2" s="6"/>
+      <c r="HN2" s="6"/>
+      <c r="HO2" s="6"/>
+      <c r="HP2" s="6"/>
+      <c r="HQ2" s="6"/>
+      <c r="HR2" s="6"/>
+      <c r="HS2" s="6"/>
+      <c r="HT2" s="6"/>
+      <c r="HU2" s="6"/>
+      <c r="HV2" s="6"/>
+      <c r="HW2" s="6"/>
+      <c r="HX2" s="6"/>
+      <c r="HY2" s="6"/>
+      <c r="HZ2" s="6"/>
+      <c r="IA2" s="6"/>
+      <c r="IB2" s="6"/>
+      <c r="IC2" s="6"/>
+      <c r="ID2" s="6"/>
+      <c r="IE2" s="6"/>
+      <c r="IF2" s="6"/>
+      <c r="IG2" s="6"/>
+      <c r="IH2" s="6"/>
+      <c r="II2" s="6"/>
+      <c r="IJ2" s="6"/>
+      <c r="IK2" s="6"/>
+      <c r="IL2" s="6"/>
+      <c r="IM2" s="6"/>
+      <c r="IN2" s="6"/>
+      <c r="IO2" s="6"/>
+      <c r="IP2" s="6"/>
+      <c r="IQ2" s="6"/>
+      <c r="IR2" s="6"/>
+      <c r="IS2" s="6"/>
+      <c r="IT2" s="6"/>
+      <c r="IU2" s="6"/>
+      <c r="IV2" s="6"/>
+      <c r="IW2" s="6"/>
+      <c r="IX2" s="6"/>
+      <c r="IY2" s="6"/>
+      <c r="IZ2" s="6"/>
+      <c r="JA2" s="6"/>
+      <c r="JB2" s="6"/>
+      <c r="JC2" s="6"/>
+      <c r="JD2" s="6"/>
+      <c r="JE2" s="6"/>
+      <c r="JF2" s="6"/>
+      <c r="JG2" s="6"/>
+      <c r="JH2" s="6"/>
+      <c r="JI2" s="6"/>
+      <c r="JJ2" s="6"/>
+      <c r="JK2" s="6"/>
+      <c r="JL2" s="6"/>
+      <c r="JM2" s="6"/>
+      <c r="JN2" s="6"/>
+      <c r="JO2" s="6"/>
+      <c r="JP2" s="6"/>
+      <c r="JQ2" s="6"/>
+      <c r="JR2" s="6"/>
+      <c r="JS2" s="6"/>
+      <c r="JT2" s="6"/>
+      <c r="JU2" s="6"/>
+      <c r="JV2" s="6"/>
+      <c r="JW2" s="6"/>
+      <c r="JX2" s="6"/>
+      <c r="JY2" s="6"/>
+      <c r="JZ2" s="6"/>
+      <c r="KA2" s="6"/>
+      <c r="KB2" s="6"/>
+      <c r="KC2" s="6"/>
+      <c r="KD2" s="6"/>
+      <c r="KE2" s="6"/>
+      <c r="KF2" s="6"/>
+      <c r="KG2" s="6"/>
+      <c r="KH2" s="6"/>
+      <c r="KI2" s="6"/>
+      <c r="KJ2" s="6"/>
+      <c r="KK2" s="6"/>
+      <c r="KL2" s="6"/>
+      <c r="KM2" s="6"/>
+      <c r="KN2" s="6"/>
+      <c r="KO2" s="6"/>
+      <c r="KP2" s="6"/>
+      <c r="KQ2" s="6"/>
+      <c r="KR2" s="6"/>
+      <c r="KS2" s="6"/>
+      <c r="KT2" s="6"/>
+      <c r="KU2" s="6"/>
+      <c r="KV2" s="6"/>
+      <c r="KW2" s="6"/>
+      <c r="KX2" s="6"/>
+      <c r="KY2" s="6"/>
+      <c r="KZ2" s="6"/>
+      <c r="LA2" s="6"/>
+      <c r="LB2" s="6"/>
+      <c r="LC2" s="6"/>
+      <c r="LD2" s="6"/>
+      <c r="LE2" s="6"/>
+      <c r="LF2" s="6"/>
+      <c r="LG2" s="6"/>
+      <c r="LH2" s="6"/>
+      <c r="LI2" s="6"/>
+      <c r="LJ2" s="6"/>
+      <c r="LK2" s="6"/>
+      <c r="LL2" s="6"/>
+      <c r="LM2" s="6"/>
+      <c r="LN2" s="6"/>
+      <c r="LO2" s="6"/>
+      <c r="LP2" s="6"/>
+      <c r="LQ2" s="6"/>
+      <c r="LR2" s="6"/>
+      <c r="LS2" s="6"/>
+      <c r="LT2" s="6"/>
+      <c r="LU2" s="6"/>
+      <c r="LV2" s="6"/>
+      <c r="LW2" s="6"/>
+      <c r="LX2" s="6"/>
+      <c r="LY2" s="6"/>
+      <c r="LZ2" s="6"/>
+      <c r="MA2" s="6"/>
+      <c r="MB2" s="6"/>
+      <c r="MC2" s="6"/>
+      <c r="MD2" s="6"/>
+      <c r="ME2" s="6"/>
+      <c r="MF2" s="6"/>
+      <c r="MG2" s="6"/>
+      <c r="MH2" s="6"/>
+      <c r="MI2" s="6"/>
+      <c r="MJ2" s="6"/>
+      <c r="MK2" s="6"/>
+      <c r="ML2" s="6"/>
+      <c r="MM2" s="6"/>
+      <c r="MN2" s="6"/>
+      <c r="MO2" s="6"/>
+      <c r="MP2" s="6"/>
+      <c r="MQ2" s="6"/>
+      <c r="MR2" s="6"/>
+      <c r="MS2" s="6"/>
+      <c r="MT2" s="6"/>
+      <c r="MU2" s="6"/>
+      <c r="MV2" s="6"/>
+      <c r="MW2" s="6"/>
+      <c r="MX2" s="6"/>
+      <c r="MY2" s="6"/>
+      <c r="MZ2" s="6"/>
+      <c r="NA2" s="6"/>
+      <c r="NB2" s="6"/>
+      <c r="NC2" s="6"/>
+      <c r="ND2" s="6"/>
+      <c r="NE2" s="6"/>
+      <c r="NF2" s="6"/>
+      <c r="NG2" s="6"/>
+      <c r="NH2" s="6"/>
+      <c r="NI2" s="6"/>
+      <c r="NJ2" s="6"/>
+      <c r="NK2" s="6"/>
+      <c r="NL2" s="6"/>
+      <c r="NM2" s="6"/>
+      <c r="NN2" s="6"/>
+      <c r="NO2" s="6"/>
+      <c r="NP2" s="6"/>
+      <c r="NQ2" s="6"/>
+      <c r="NR2" s="6"/>
+      <c r="NS2" s="6"/>
+      <c r="NT2" s="6"/>
+      <c r="NU2" s="6"/>
+      <c r="NV2" s="6"/>
+      <c r="NW2" s="6"/>
+      <c r="NX2" s="6"/>
+      <c r="NY2" s="6"/>
+      <c r="NZ2" s="6"/>
+      <c r="OA2" s="6"/>
+      <c r="OB2" s="6"/>
+      <c r="OC2" s="6"/>
+      <c r="OD2" s="6"/>
+      <c r="OE2" s="6"/>
+      <c r="OF2" s="6"/>
+      <c r="OG2" s="6"/>
+      <c r="OH2" s="6"/>
+      <c r="OI2" s="6"/>
+      <c r="OJ2" s="6"/>
+      <c r="OK2" s="6"/>
+      <c r="OL2" s="6"/>
+      <c r="OM2" s="6"/>
+      <c r="ON2" s="6"/>
+      <c r="OO2" s="6"/>
+      <c r="OP2" s="6"/>
+      <c r="OQ2" s="6"/>
+      <c r="OR2" s="6"/>
+      <c r="OS2" s="6"/>
+      <c r="OT2" s="6"/>
+      <c r="OU2" s="6"/>
+      <c r="OV2" s="6"/>
+      <c r="OW2" s="6"/>
+      <c r="OX2" s="6"/>
+      <c r="OY2" s="6"/>
+      <c r="OZ2" s="6"/>
+      <c r="PA2" s="6"/>
+      <c r="PB2" s="6"/>
+      <c r="PC2" s="6"/>
+      <c r="PD2" s="6"/>
+      <c r="PE2" s="6"/>
+      <c r="PF2" s="6"/>
+      <c r="PG2" s="6"/>
+      <c r="PH2" s="6"/>
+      <c r="PI2" s="6"/>
+      <c r="PJ2" s="6"/>
+      <c r="PK2" s="6"/>
+      <c r="PL2" s="6"/>
+      <c r="PM2" s="6"/>
+      <c r="PN2" s="6"/>
+      <c r="PO2" s="6"/>
+      <c r="PP2" s="6"/>
+      <c r="PQ2" s="6"/>
+      <c r="PR2" s="6"/>
+      <c r="PS2" s="6"/>
+      <c r="PT2" s="6"/>
+      <c r="PU2" s="6"/>
+      <c r="PV2" s="6"/>
+      <c r="PW2" s="6"/>
+      <c r="PX2" s="6"/>
+      <c r="PY2" s="6"/>
+      <c r="PZ2" s="6"/>
+      <c r="QA2" s="6"/>
+      <c r="QB2" s="6"/>
+      <c r="QC2" s="6"/>
+      <c r="QD2" s="6"/>
+      <c r="QE2" s="6"/>
+      <c r="QF2" s="6"/>
+      <c r="QG2" s="6"/>
+      <c r="QH2" s="6"/>
+      <c r="QI2" s="6"/>
+      <c r="QJ2" s="6"/>
+      <c r="QK2" s="6"/>
+      <c r="QL2" s="6"/>
+      <c r="QM2" s="6"/>
+      <c r="QN2" s="6"/>
+      <c r="QO2" s="6"/>
+      <c r="QP2" s="6"/>
+      <c r="QQ2" s="6"/>
+      <c r="QR2" s="6"/>
+      <c r="QS2" s="6"/>
+      <c r="QT2" s="6"/>
+      <c r="QU2" s="6"/>
+      <c r="QV2" s="6"/>
+      <c r="QW2" s="6"/>
+      <c r="QX2" s="6"/>
+      <c r="QY2" s="6"/>
+      <c r="QZ2" s="6"/>
+      <c r="RA2" s="6"/>
+      <c r="RB2" s="6"/>
+      <c r="RC2" s="6"/>
+      <c r="RD2" s="6"/>
+      <c r="RE2" s="6"/>
+      <c r="RF2" s="6"/>
+      <c r="RG2" s="6"/>
+      <c r="RH2" s="6"/>
+      <c r="RI2" s="6"/>
+      <c r="RJ2" s="6"/>
+      <c r="RK2" s="6"/>
+      <c r="RL2" s="6"/>
+      <c r="RM2" s="6"/>
+      <c r="RN2" s="6"/>
+      <c r="RO2" s="6"/>
+      <c r="RP2" s="6"/>
+      <c r="RQ2" s="6"/>
+      <c r="RR2" s="6"/>
+      <c r="RS2" s="6"/>
+      <c r="RT2" s="6"/>
+      <c r="RU2" s="6"/>
+      <c r="RV2" s="6"/>
+      <c r="RW2" s="6"/>
+      <c r="RX2" s="6"/>
+      <c r="RY2" s="6"/>
+      <c r="RZ2" s="6"/>
+      <c r="SA2" s="6"/>
+      <c r="SB2" s="6"/>
+      <c r="SC2" s="6"/>
+      <c r="SD2" s="6"/>
+      <c r="SE2" s="6"/>
+      <c r="SF2" s="6"/>
+      <c r="SG2" s="6"/>
+      <c r="SH2" s="6"/>
+      <c r="SI2" s="6"/>
+      <c r="SJ2" s="6"/>
+      <c r="SK2" s="6"/>
+      <c r="SL2" s="6"/>
+      <c r="SM2" s="6"/>
+      <c r="SN2" s="6"/>
+      <c r="SO2" s="6"/>
+      <c r="SP2" s="6"/>
+      <c r="SQ2" s="6"/>
+      <c r="SR2" s="6"/>
+      <c r="SS2" s="6"/>
+      <c r="ST2" s="6"/>
+      <c r="SU2" s="6"/>
+      <c r="SV2" s="6"/>
+      <c r="SW2" s="6"/>
+      <c r="SX2" s="6"/>
+      <c r="SY2" s="6"/>
+      <c r="SZ2" s="6"/>
+      <c r="TA2" s="6"/>
+      <c r="TB2" s="6"/>
+      <c r="TC2" s="6"/>
+      <c r="TD2" s="6"/>
+      <c r="TE2" s="6"/>
+      <c r="TF2" s="6"/>
+      <c r="TG2" s="6"/>
+      <c r="TH2" s="6"/>
+      <c r="TI2" s="6"/>
+      <c r="TJ2" s="6"/>
+      <c r="TK2" s="6"/>
+      <c r="TL2" s="6"/>
+      <c r="TM2" s="6"/>
+      <c r="TN2" s="6"/>
+      <c r="TO2" s="6"/>
+      <c r="TP2" s="6"/>
+      <c r="TQ2" s="6"/>
+      <c r="TR2" s="6"/>
+      <c r="TS2" s="6"/>
+      <c r="TT2" s="6"/>
+      <c r="TU2" s="6"/>
+      <c r="TV2" s="6"/>
+      <c r="TW2" s="6"/>
+      <c r="TX2" s="6"/>
+      <c r="TY2" s="6"/>
+      <c r="TZ2" s="6"/>
+      <c r="UA2" s="6"/>
+      <c r="UB2" s="6"/>
+      <c r="UC2" s="6"/>
+      <c r="UD2" s="6"/>
+      <c r="UE2" s="6"/>
+      <c r="UF2" s="6"/>
+      <c r="UG2" s="6"/>
+      <c r="UH2" s="6"/>
+      <c r="UI2" s="6"/>
+      <c r="UJ2" s="6"/>
+      <c r="UK2" s="6"/>
+      <c r="UL2" s="6"/>
+      <c r="UM2" s="6"/>
+      <c r="UN2" s="6"/>
+      <c r="UO2" s="6"/>
+      <c r="UP2" s="6"/>
+      <c r="UQ2" s="6"/>
+      <c r="UR2" s="6"/>
+      <c r="US2" s="6"/>
+      <c r="UT2" s="6"/>
+      <c r="UU2" s="6"/>
+      <c r="UV2" s="6"/>
+      <c r="UW2" s="6"/>
+      <c r="UX2" s="6"/>
+      <c r="UY2" s="6"/>
+      <c r="UZ2" s="6"/>
+      <c r="VA2" s="6"/>
+      <c r="VB2" s="6"/>
+      <c r="VC2" s="6"/>
+      <c r="VD2" s="6"/>
+      <c r="VE2" s="6"/>
+      <c r="VF2" s="6"/>
+      <c r="VG2" s="6"/>
+      <c r="VH2" s="6"/>
+      <c r="VI2" s="6"/>
+      <c r="VJ2" s="6"/>
+      <c r="VK2" s="6"/>
+      <c r="VL2" s="6"/>
+      <c r="VM2" s="6"/>
+      <c r="VN2" s="6"/>
+      <c r="VO2" s="6"/>
+      <c r="VP2" s="6"/>
+      <c r="VQ2" s="6"/>
+      <c r="VR2" s="6"/>
+      <c r="VS2" s="6"/>
+      <c r="VT2" s="6"/>
+      <c r="VU2" s="6"/>
+      <c r="VV2" s="6"/>
+      <c r="VW2" s="6"/>
+      <c r="VX2" s="6"/>
+      <c r="VY2" s="6"/>
+      <c r="VZ2" s="6"/>
+      <c r="WA2" s="6"/>
+      <c r="WB2" s="6"/>
+      <c r="WC2" s="6"/>
+      <c r="WD2" s="6"/>
+      <c r="WE2" s="6"/>
+      <c r="WF2" s="6"/>
+      <c r="WG2" s="6"/>
+      <c r="WH2" s="6"/>
+      <c r="WI2" s="6"/>
+      <c r="WJ2" s="6"/>
+      <c r="WK2" s="6"/>
+      <c r="WL2" s="6"/>
+      <c r="WM2" s="6"/>
+      <c r="WN2" s="6"/>
+      <c r="WO2" s="6"/>
+      <c r="WP2" s="6"/>
+      <c r="WQ2" s="6"/>
+      <c r="WR2" s="6"/>
+      <c r="WS2" s="6"/>
+      <c r="WT2" s="6"/>
+      <c r="WU2" s="6"/>
+      <c r="WV2" s="6"/>
+      <c r="WW2" s="6"/>
+      <c r="WX2" s="6"/>
+      <c r="WY2" s="6"/>
+      <c r="WZ2" s="6"/>
+      <c r="XA2" s="6"/>
+      <c r="XB2" s="6"/>
+      <c r="XC2" s="6"/>
+      <c r="XD2" s="6"/>
+      <c r="XE2" s="6"/>
+      <c r="XF2" s="6"/>
+      <c r="XG2" s="6"/>
+      <c r="XH2" s="6"/>
+      <c r="XI2" s="6"/>
+      <c r="XJ2" s="6"/>
+      <c r="XK2" s="6"/>
+      <c r="XL2" s="6"/>
+      <c r="XM2" s="6"/>
+      <c r="XN2" s="6"/>
+      <c r="XO2" s="6"/>
+      <c r="XP2" s="6"/>
+      <c r="XQ2" s="6"/>
+      <c r="XR2" s="6"/>
+      <c r="XS2" s="6"/>
+      <c r="XT2" s="6"/>
+      <c r="XU2" s="6"/>
+      <c r="XV2" s="6"/>
+      <c r="XW2" s="6"/>
+      <c r="XX2" s="6"/>
+      <c r="XY2" s="6"/>
+      <c r="XZ2" s="6"/>
+      <c r="YA2" s="6"/>
+      <c r="YB2" s="6"/>
+      <c r="YC2" s="6"/>
+      <c r="YD2" s="6"/>
+      <c r="YE2" s="6"/>
+      <c r="YF2" s="6"/>
+      <c r="YG2" s="6"/>
+      <c r="YH2" s="6"/>
+      <c r="YI2" s="6"/>
+      <c r="YJ2" s="6"/>
+      <c r="YK2" s="6"/>
+      <c r="YL2" s="6"/>
+      <c r="YM2" s="6"/>
+      <c r="YN2" s="6"/>
+      <c r="YO2" s="6"/>
+      <c r="YP2" s="6"/>
+      <c r="YQ2" s="6"/>
+      <c r="YR2" s="6"/>
+      <c r="YS2" s="6"/>
+      <c r="YT2" s="6"/>
+      <c r="YU2" s="6"/>
+      <c r="YV2" s="6"/>
+      <c r="YW2" s="6"/>
+      <c r="YX2" s="6"/>
+      <c r="YY2" s="6"/>
+      <c r="YZ2" s="6"/>
+      <c r="ZA2" s="6"/>
+      <c r="ZB2" s="6"/>
+      <c r="ZC2" s="6"/>
+      <c r="ZD2" s="6"/>
+      <c r="ZE2" s="6"/>
+      <c r="ZF2" s="6"/>
+      <c r="ZG2" s="6"/>
+      <c r="ZH2" s="6"/>
+      <c r="ZI2" s="6"/>
+      <c r="ZJ2" s="6"/>
+      <c r="ZK2" s="6"/>
+      <c r="ZL2" s="6"/>
+      <c r="ZM2" s="6"/>
+      <c r="ZN2" s="6"/>
+      <c r="ZO2" s="6"/>
+      <c r="ZP2" s="6"/>
+      <c r="ZQ2" s="6"/>
+      <c r="ZR2" s="6"/>
+      <c r="ZS2" s="6"/>
+      <c r="ZT2" s="6"/>
+      <c r="ZU2" s="6"/>
+      <c r="ZV2" s="6"/>
+      <c r="ZW2" s="6"/>
+      <c r="ZX2" s="6"/>
+      <c r="ZY2" s="6"/>
+      <c r="ZZ2" s="6"/>
+      <c r="AAA2" s="6"/>
+      <c r="AAB2" s="6"/>
+      <c r="AAC2" s="6"/>
+      <c r="AAD2" s="6"/>
+      <c r="AAE2" s="6"/>
+      <c r="AAF2" s="6"/>
+      <c r="AAG2" s="6"/>
+      <c r="AAH2" s="6"/>
+      <c r="AAI2" s="6"/>
+      <c r="AAJ2" s="6"/>
+      <c r="AAK2" s="6"/>
+      <c r="AAL2" s="6"/>
+      <c r="AAM2" s="6"/>
+      <c r="AAN2" s="6"/>
+      <c r="AAO2" s="6"/>
+      <c r="AAP2" s="6"/>
+      <c r="AAQ2" s="6"/>
+      <c r="AAR2" s="6"/>
+      <c r="AAS2" s="6"/>
+      <c r="AAT2" s="6"/>
+      <c r="AAU2" s="6"/>
+      <c r="AAV2" s="6"/>
+      <c r="AAW2" s="6"/>
+      <c r="AAX2" s="6"/>
+      <c r="AAY2" s="6"/>
+      <c r="AAZ2" s="6"/>
+      <c r="ABA2" s="6"/>
+      <c r="ABB2" s="6"/>
+      <c r="ABC2" s="6"/>
+      <c r="ABD2" s="6"/>
+      <c r="ABE2" s="6"/>
+      <c r="ABF2" s="6"/>
+      <c r="ABG2" s="6"/>
+      <c r="ABH2" s="6"/>
+      <c r="ABI2" s="6"/>
+      <c r="ABJ2" s="6"/>
+      <c r="ABK2" s="6"/>
+      <c r="ABL2" s="6"/>
+      <c r="ABM2" s="6"/>
+      <c r="ABN2" s="6"/>
+      <c r="ABO2" s="6"/>
+      <c r="ABP2" s="6"/>
+      <c r="ABQ2" s="6"/>
+      <c r="ABR2" s="6"/>
+      <c r="ABS2" s="6"/>
+      <c r="ABT2" s="6"/>
+      <c r="ABU2" s="6"/>
+      <c r="ABV2" s="6"/>
+      <c r="ABW2" s="6"/>
+      <c r="ABX2" s="6"/>
+      <c r="ABY2" s="6"/>
+      <c r="ABZ2" s="6"/>
+      <c r="ACA2" s="6"/>
+      <c r="ACB2" s="6"/>
+      <c r="ACC2" s="6"/>
+      <c r="ACD2" s="6"/>
+      <c r="ACE2" s="6"/>
+      <c r="ACF2" s="6"/>
+      <c r="ACG2" s="6"/>
+      <c r="ACH2" s="6"/>
+      <c r="ACI2" s="6"/>
+      <c r="ACJ2" s="6"/>
+      <c r="ACK2" s="6"/>
+      <c r="ACL2" s="6"/>
+      <c r="ACM2" s="6"/>
+      <c r="ACN2" s="6"/>
+      <c r="ACO2" s="6"/>
+      <c r="ACP2" s="6"/>
+      <c r="ACQ2" s="6"/>
+      <c r="ACR2" s="6"/>
+      <c r="ACS2" s="6"/>
+      <c r="ACT2" s="6"/>
+      <c r="ACU2" s="6"/>
+      <c r="ACV2" s="6"/>
+      <c r="ACW2" s="6"/>
+      <c r="ACX2" s="6"/>
+      <c r="ACY2" s="6"/>
+      <c r="ACZ2" s="6"/>
+      <c r="ADA2" s="6"/>
+      <c r="ADB2" s="6"/>
+      <c r="ADC2" s="6"/>
+      <c r="ADD2" s="6"/>
+      <c r="ADE2" s="6"/>
+      <c r="ADF2" s="6"/>
+      <c r="ADG2" s="6"/>
+      <c r="ADH2" s="6"/>
+      <c r="ADI2" s="6"/>
+      <c r="ADJ2" s="6"/>
+      <c r="ADK2" s="6"/>
+      <c r="ADL2" s="6"/>
+      <c r="ADM2" s="6"/>
+      <c r="ADN2" s="6"/>
+      <c r="ADO2" s="6"/>
+      <c r="ADP2" s="6"/>
+      <c r="ADQ2" s="6"/>
+      <c r="ADR2" s="6"/>
+      <c r="ADS2" s="6"/>
+      <c r="ADT2" s="6"/>
+      <c r="ADU2" s="6"/>
+      <c r="ADV2" s="6"/>
+      <c r="ADW2" s="6"/>
+      <c r="ADX2" s="6"/>
+      <c r="ADY2" s="6"/>
+      <c r="ADZ2" s="6"/>
+      <c r="AEA2" s="6"/>
+      <c r="AEB2" s="6"/>
+      <c r="AEC2" s="6"/>
+      <c r="AED2" s="6"/>
+      <c r="AEE2" s="6"/>
+      <c r="AEF2" s="6"/>
+      <c r="AEG2" s="6"/>
+      <c r="AEH2" s="6"/>
+      <c r="AEI2" s="6"/>
+      <c r="AEJ2" s="6"/>
+      <c r="AEK2" s="6"/>
+      <c r="AEL2" s="6"/>
+      <c r="AEM2" s="6"/>
+      <c r="AEN2" s="6"/>
+      <c r="AEO2" s="6"/>
+      <c r="AEP2" s="6"/>
+      <c r="AEQ2" s="6"/>
+      <c r="AER2" s="6"/>
+      <c r="AES2" s="6"/>
+      <c r="AET2" s="6"/>
+      <c r="AEU2" s="6"/>
+      <c r="AEV2" s="6"/>
+      <c r="AEW2" s="6"/>
+      <c r="AEX2" s="6"/>
+      <c r="AEY2" s="6"/>
+      <c r="AEZ2" s="6"/>
+      <c r="AFA2" s="6"/>
+      <c r="AFB2" s="6"/>
+      <c r="AFC2" s="6"/>
+      <c r="AFD2" s="6"/>
+      <c r="AFE2" s="6"/>
+      <c r="AFF2" s="6"/>
+      <c r="AFG2" s="6"/>
+      <c r="AFH2" s="6"/>
+      <c r="AFI2" s="6"/>
+      <c r="AFJ2" s="6"/>
+      <c r="AFK2" s="6"/>
+      <c r="AFL2" s="6"/>
+      <c r="AFM2" s="6"/>
+      <c r="AFN2" s="6"/>
+      <c r="AFO2" s="6"/>
+      <c r="AFP2" s="6"/>
+      <c r="AFQ2" s="6"/>
+      <c r="AFR2" s="6"/>
+      <c r="AFS2" s="6"/>
+      <c r="AFT2" s="6"/>
+      <c r="AFU2" s="6"/>
+      <c r="AFV2" s="6"/>
+      <c r="AFW2" s="6"/>
+      <c r="AFX2" s="6"/>
+      <c r="AFY2" s="6"/>
+      <c r="AFZ2" s="6"/>
+      <c r="AGA2" s="6"/>
+      <c r="AGB2" s="6"/>
+      <c r="AGC2" s="6"/>
+      <c r="AGD2" s="6"/>
+      <c r="AGE2" s="6"/>
+      <c r="AGF2" s="6"/>
+      <c r="AGG2" s="6"/>
+      <c r="AGH2" s="6"/>
+      <c r="AGI2" s="6"/>
+      <c r="AGJ2" s="6"/>
+      <c r="AGK2" s="6"/>
+      <c r="AGL2" s="6"/>
+      <c r="AGM2" s="6"/>
+      <c r="AGN2" s="6"/>
+      <c r="AGO2" s="6"/>
+      <c r="AGP2" s="6"/>
+      <c r="AGQ2" s="6"/>
+      <c r="AGR2" s="6"/>
+      <c r="AGS2" s="6"/>
+      <c r="AGT2" s="6"/>
+      <c r="AGU2" s="6"/>
+      <c r="AGV2" s="6"/>
+      <c r="AGW2" s="6"/>
+      <c r="AGX2" s="6"/>
+      <c r="AGY2" s="6"/>
+      <c r="AGZ2" s="6"/>
+      <c r="AHA2" s="6"/>
+      <c r="AHB2" s="6"/>
+      <c r="AHC2" s="6"/>
+      <c r="AHD2" s="6"/>
+      <c r="AHE2" s="6"/>
+      <c r="AHF2" s="6"/>
+      <c r="AHG2" s="6"/>
+      <c r="AHH2" s="6"/>
+      <c r="AHI2" s="6"/>
+      <c r="AHJ2" s="6"/>
+      <c r="AHK2" s="6"/>
+      <c r="AHL2" s="6"/>
+      <c r="AHM2" s="6"/>
+      <c r="AHN2" s="6"/>
+      <c r="AHO2" s="6"/>
+      <c r="AHP2" s="6"/>
+      <c r="AHQ2" s="6"/>
+      <c r="AHR2" s="6"/>
+      <c r="AHS2" s="6"/>
+      <c r="AHT2" s="6"/>
+      <c r="AHU2" s="6"/>
+      <c r="AHV2" s="6"/>
+      <c r="AHW2" s="6"/>
+      <c r="AHX2" s="6"/>
+      <c r="AHY2" s="6"/>
+      <c r="AHZ2" s="6"/>
+      <c r="AIA2" s="6"/>
+      <c r="AIB2" s="6"/>
+      <c r="AIC2" s="6"/>
+      <c r="AID2" s="6"/>
+      <c r="AIE2" s="6"/>
+      <c r="AIF2" s="6"/>
+      <c r="AIG2" s="6"/>
+      <c r="AIH2" s="6"/>
+      <c r="AII2" s="6"/>
+      <c r="AIJ2" s="6"/>
+      <c r="AIK2" s="6"/>
+      <c r="AIL2" s="6"/>
+      <c r="AIM2" s="6"/>
+      <c r="AIN2" s="6"/>
+      <c r="AIO2" s="6"/>
+      <c r="AIP2" s="6"/>
+      <c r="AIQ2" s="6"/>
+      <c r="AIR2" s="6"/>
+      <c r="AIS2" s="6"/>
+      <c r="AIT2" s="6"/>
+      <c r="AIU2" s="6"/>
+      <c r="AIV2" s="6"/>
+      <c r="AIW2" s="6"/>
+      <c r="AIX2" s="6"/>
+      <c r="AIY2" s="6"/>
+      <c r="AIZ2" s="6"/>
+      <c r="AJA2" s="6"/>
+      <c r="AJB2" s="6"/>
+      <c r="AJC2" s="6"/>
+      <c r="AJD2" s="6"/>
+      <c r="AJE2" s="6"/>
+      <c r="AJF2" s="6"/>
+      <c r="AJG2" s="6"/>
+      <c r="AJH2" s="6"/>
+      <c r="AJI2" s="6"/>
+      <c r="AJJ2" s="6"/>
+      <c r="AJK2" s="6"/>
+      <c r="AJL2" s="6"/>
+      <c r="AJM2" s="6"/>
+      <c r="AJN2" s="6"/>
+      <c r="AJO2" s="6"/>
+      <c r="AJP2" s="6"/>
+      <c r="AJQ2" s="6"/>
+      <c r="AJR2" s="6"/>
+      <c r="AJS2" s="6"/>
+      <c r="AJT2" s="6"/>
+      <c r="AJU2" s="6"/>
+      <c r="AJV2" s="6"/>
+      <c r="AJW2" s="6"/>
+      <c r="AJX2" s="6"/>
+      <c r="AJY2" s="6"/>
+      <c r="AJZ2" s="6"/>
+      <c r="AKA2" s="6"/>
+      <c r="AKB2" s="6"/>
+      <c r="AKC2" s="6"/>
+      <c r="AKD2" s="6"/>
+      <c r="AKE2" s="6"/>
+      <c r="AKF2" s="6"/>
+      <c r="AKG2" s="6"/>
+      <c r="AKH2" s="6"/>
+      <c r="AKI2" s="6"/>
+      <c r="AKJ2" s="6"/>
+      <c r="AKK2" s="6"/>
+      <c r="AKL2" s="6"/>
+      <c r="AKM2" s="6"/>
+      <c r="AKN2" s="6"/>
+      <c r="AKO2" s="6"/>
+      <c r="AKP2" s="6"/>
+      <c r="AKQ2" s="6"/>
+      <c r="AKR2" s="6"/>
+      <c r="AKS2" s="6"/>
+      <c r="AKT2" s="6"/>
+      <c r="AKU2" s="6"/>
+      <c r="AKV2" s="6"/>
+      <c r="AKW2" s="6"/>
+      <c r="AKX2" s="6"/>
+      <c r="AKY2" s="6"/>
+      <c r="AKZ2" s="6"/>
+      <c r="ALA2" s="6"/>
+      <c r="ALB2" s="6"/>
+      <c r="ALC2" s="6"/>
+      <c r="ALD2" s="6"/>
+      <c r="ALE2" s="6"/>
+      <c r="ALF2" s="6"/>
+      <c r="ALG2" s="6"/>
+      <c r="ALH2" s="6"/>
+      <c r="ALI2" s="6"/>
+      <c r="ALJ2" s="6"/>
+      <c r="ALK2" s="6"/>
+      <c r="ALL2" s="6"/>
+      <c r="ALM2" s="6"/>
+      <c r="ALN2" s="6"/>
+      <c r="ALO2" s="6"/>
+      <c r="ALP2" s="6"/>
+      <c r="ALQ2" s="6"/>
+      <c r="ALR2" s="6"/>
+      <c r="ALS2" s="6"/>
+      <c r="ALT2" s="6"/>
+      <c r="ALU2" s="6"/>
+      <c r="ALV2" s="6"/>
+      <c r="ALW2" s="6"/>
+      <c r="ALX2" s="6"/>
+      <c r="ALY2" s="6"/>
+      <c r="ALZ2" s="6"/>
+      <c r="AMA2" s="6"/>
+      <c r="AMB2" s="6"/>
+      <c r="AMC2" s="6"/>
+      <c r="AMD2" s="6"/>
+      <c r="AME2" s="6"/>
+      <c r="AMF2" s="6"/>
+      <c r="AMG2" s="6"/>
+      <c r="AMH2" s="6"/>
+      <c r="AMI2" s="6"/>
+      <c r="AMJ2" s="6"/>
+      <c r="AMK2" s="6"/>
+      <c r="AML2" s="6"/>
+      <c r="AMM2" s="6"/>
+      <c r="AMN2" s="6"/>
+      <c r="AMO2" s="6"/>
+      <c r="AMP2" s="6"/>
+      <c r="AMQ2" s="6"/>
+      <c r="AMR2" s="6"/>
+      <c r="AMS2" s="6"/>
+      <c r="AMT2" s="6"/>
+      <c r="AMU2" s="6"/>
+      <c r="AMV2" s="6"/>
+      <c r="AMW2" s="6"/>
+      <c r="AMX2" s="6"/>
+      <c r="AMY2" s="6"/>
+      <c r="AMZ2" s="6"/>
+      <c r="ANA2" s="6"/>
+      <c r="ANB2" s="6"/>
+      <c r="ANC2" s="6"/>
+      <c r="AND2" s="6"/>
+      <c r="ANE2" s="6"/>
+      <c r="ANF2" s="6"/>
+      <c r="ANG2" s="6"/>
+      <c r="ANH2" s="6"/>
+      <c r="ANI2" s="6"/>
+      <c r="ANJ2" s="6"/>
+      <c r="ANK2" s="6"/>
+      <c r="ANL2" s="6"/>
+      <c r="ANM2" s="6"/>
+      <c r="ANN2" s="6"/>
+      <c r="ANO2" s="6"/>
+      <c r="ANP2" s="6"/>
+      <c r="ANQ2" s="6"/>
+      <c r="ANR2" s="6"/>
+      <c r="ANS2" s="6"/>
+      <c r="ANT2" s="6"/>
+      <c r="ANU2" s="6"/>
+      <c r="ANV2" s="6"/>
+      <c r="ANW2" s="6"/>
+      <c r="ANX2" s="6"/>
+      <c r="ANY2" s="6"/>
+      <c r="ANZ2" s="6"/>
+      <c r="AOA2" s="6"/>
+      <c r="AOB2" s="6"/>
+      <c r="AOC2" s="6"/>
+      <c r="AOD2" s="6"/>
+      <c r="AOE2" s="6"/>
+      <c r="AOF2" s="6"/>
+      <c r="AOG2" s="6"/>
+      <c r="AOH2" s="6"/>
+      <c r="AOI2" s="6"/>
+      <c r="AOJ2" s="6"/>
+      <c r="AOK2" s="6"/>
+      <c r="AOL2" s="6"/>
+      <c r="AOM2" s="6"/>
+      <c r="AON2" s="6"/>
+      <c r="AOO2" s="6"/>
+      <c r="AOP2" s="6"/>
+      <c r="AOQ2" s="6"/>
+      <c r="AOR2" s="6"/>
+      <c r="AOS2" s="6"/>
+      <c r="AOT2" s="6"/>
+      <c r="AOU2" s="6"/>
+      <c r="AOV2" s="6"/>
+      <c r="AOW2" s="6"/>
+      <c r="AOX2" s="6"/>
+      <c r="AOY2" s="6"/>
+      <c r="AOZ2" s="6"/>
+      <c r="APA2" s="6"/>
+      <c r="APB2" s="6"/>
+      <c r="APC2" s="6"/>
+      <c r="APD2" s="6"/>
+      <c r="APE2" s="6"/>
+      <c r="APF2" s="6"/>
+      <c r="APG2" s="6"/>
+      <c r="APH2" s="6"/>
+      <c r="API2" s="6"/>
+      <c r="APJ2" s="6"/>
+      <c r="APK2" s="6"/>
+      <c r="APL2" s="6"/>
+      <c r="APM2" s="6"/>
+      <c r="APN2" s="6"/>
+      <c r="APO2" s="6"/>
+      <c r="APP2" s="6"/>
+      <c r="APQ2" s="6"/>
+      <c r="APR2" s="6"/>
+      <c r="APS2" s="6"/>
+      <c r="APT2" s="6"/>
+      <c r="APU2" s="6"/>
+      <c r="APV2" s="6"/>
+      <c r="APW2" s="6"/>
+      <c r="APX2" s="6"/>
+      <c r="APY2" s="6"/>
+      <c r="APZ2" s="6"/>
+      <c r="AQA2" s="6"/>
+      <c r="AQB2" s="6"/>
+      <c r="AQC2" s="6"/>
+      <c r="AQD2" s="6"/>
+      <c r="AQE2" s="6"/>
+      <c r="AQF2" s="6"/>
+      <c r="AQG2" s="6"/>
+      <c r="AQH2" s="6"/>
+      <c r="AQI2" s="6"/>
+      <c r="AQJ2" s="6"/>
+      <c r="AQK2" s="6"/>
+      <c r="AQL2" s="6"/>
+      <c r="AQM2" s="6"/>
+      <c r="AQN2" s="6"/>
+      <c r="AQO2" s="6"/>
+      <c r="AQP2" s="6"/>
+      <c r="AQQ2" s="6"/>
+      <c r="AQR2" s="6"/>
+      <c r="AQS2" s="6"/>
+      <c r="AQT2" s="6"/>
+      <c r="AQU2" s="6"/>
+      <c r="AQV2" s="6"/>
+      <c r="AQW2" s="6"/>
+      <c r="AQX2" s="6"/>
+      <c r="AQY2" s="6"/>
+      <c r="AQZ2" s="6"/>
+      <c r="ARA2" s="6"/>
+      <c r="ARB2" s="6"/>
+      <c r="ARC2" s="6"/>
+      <c r="ARD2" s="6"/>
+      <c r="ARE2" s="6"/>
+      <c r="ARF2" s="6"/>
+      <c r="ARG2" s="6"/>
+      <c r="ARH2" s="6"/>
+      <c r="ARI2" s="6"/>
+      <c r="ARJ2" s="6"/>
+      <c r="ARK2" s="6"/>
+      <c r="ARL2" s="6"/>
+      <c r="ARM2" s="6"/>
+      <c r="ARN2" s="6"/>
+      <c r="ARO2" s="6"/>
+      <c r="ARP2" s="6"/>
+      <c r="ARQ2" s="6"/>
+      <c r="ARR2" s="6"/>
+      <c r="ARS2" s="6"/>
+      <c r="ART2" s="6"/>
+      <c r="ARU2" s="6"/>
+      <c r="ARV2" s="6"/>
+      <c r="ARW2" s="6"/>
+      <c r="ARX2" s="6"/>
+      <c r="ARY2" s="6"/>
+      <c r="ARZ2" s="6"/>
+      <c r="ASA2" s="6"/>
+      <c r="ASB2" s="6"/>
+      <c r="ASC2" s="6"/>
+      <c r="ASD2" s="6"/>
+      <c r="ASE2" s="6"/>
+      <c r="ASF2" s="6"/>
+      <c r="ASG2" s="6"/>
+      <c r="ASH2" s="6"/>
+      <c r="ASI2" s="6"/>
+      <c r="ASJ2" s="6"/>
+      <c r="ASK2" s="6"/>
+      <c r="ASL2" s="6"/>
+      <c r="ASM2" s="6"/>
+      <c r="ASN2" s="6"/>
+      <c r="ASO2" s="6"/>
+      <c r="ASP2" s="6"/>
+      <c r="ASQ2" s="6"/>
+      <c r="ASR2" s="6"/>
+      <c r="ASS2" s="6"/>
+      <c r="AST2" s="6"/>
+      <c r="ASU2" s="6"/>
+      <c r="ASV2" s="6"/>
+      <c r="ASW2" s="6"/>
+      <c r="ASX2" s="6"/>
+      <c r="ASY2" s="6"/>
+      <c r="ASZ2" s="6"/>
+      <c r="ATA2" s="6"/>
+      <c r="ATB2" s="6"/>
+      <c r="ATC2" s="6"/>
+      <c r="ATD2" s="6"/>
+      <c r="ATE2" s="6"/>
+      <c r="ATF2" s="6"/>
+      <c r="ATG2" s="6"/>
+      <c r="ATH2" s="6"/>
+      <c r="ATI2" s="6"/>
+      <c r="ATJ2" s="6"/>
+      <c r="ATK2" s="6"/>
+      <c r="ATL2" s="6"/>
+      <c r="ATM2" s="6"/>
+      <c r="ATN2" s="6"/>
+      <c r="ATO2" s="6"/>
+      <c r="ATP2" s="6"/>
+      <c r="ATQ2" s="6"/>
+      <c r="ATR2" s="6"/>
+      <c r="ATS2" s="6"/>
+      <c r="ATT2" s="6"/>
+      <c r="ATU2" s="6"/>
+      <c r="ATV2" s="6"/>
+      <c r="ATW2" s="6"/>
+      <c r="ATX2" s="6"/>
+      <c r="ATY2" s="6"/>
+      <c r="ATZ2" s="6"/>
+      <c r="AUA2" s="6"/>
+      <c r="AUB2" s="6"/>
+      <c r="AUC2" s="6"/>
+      <c r="AUD2" s="6"/>
+      <c r="AUE2" s="6"/>
+      <c r="AUF2" s="6"/>
+      <c r="AUG2" s="6"/>
+      <c r="AUH2" s="6"/>
+      <c r="AUI2" s="6"/>
+      <c r="AUJ2" s="6"/>
+      <c r="AUK2" s="6"/>
+      <c r="AUL2" s="6"/>
+      <c r="AUM2" s="6"/>
+      <c r="AUN2" s="6"/>
+      <c r="AUO2" s="6"/>
+      <c r="AUP2" s="6"/>
+      <c r="AUQ2" s="6"/>
+      <c r="AUR2" s="6"/>
+      <c r="AUS2" s="6"/>
+      <c r="AUT2" s="6"/>
+      <c r="AUU2" s="6"/>
+      <c r="AUV2" s="6"/>
+      <c r="AUW2" s="6"/>
+      <c r="AUX2" s="6"/>
+      <c r="AUY2" s="6"/>
+      <c r="AUZ2" s="6"/>
+      <c r="AVA2" s="6"/>
+      <c r="AVB2" s="6"/>
+      <c r="AVC2" s="6"/>
+      <c r="AVD2" s="6"/>
+      <c r="AVE2" s="6"/>
+      <c r="AVF2" s="6"/>
+      <c r="AVG2" s="6"/>
+      <c r="AVH2" s="6"/>
+      <c r="AVI2" s="6"/>
+      <c r="AVJ2" s="6"/>
+      <c r="AVK2" s="6"/>
+      <c r="AVL2" s="6"/>
+      <c r="AVM2" s="6"/>
+      <c r="AVN2" s="6"/>
+      <c r="AVO2" s="6"/>
+      <c r="AVP2" s="6"/>
+      <c r="AVQ2" s="6"/>
+      <c r="AVR2" s="6"/>
+      <c r="AVS2" s="6"/>
+      <c r="AVT2" s="6"/>
+      <c r="AVU2" s="6"/>
+      <c r="AVV2" s="6"/>
+      <c r="AVW2" s="6"/>
+      <c r="AVX2" s="6"/>
+      <c r="AVY2" s="6"/>
+      <c r="AVZ2" s="6"/>
+      <c r="AWA2" s="6"/>
+      <c r="AWB2" s="6"/>
+      <c r="AWC2" s="6"/>
+      <c r="AWD2" s="6"/>
+      <c r="AWE2" s="6"/>
+      <c r="AWF2" s="6"/>
+      <c r="AWG2" s="6"/>
+      <c r="AWH2" s="6"/>
+      <c r="AWI2" s="6"/>
+      <c r="AWJ2" s="6"/>
+      <c r="AWK2" s="6"/>
+      <c r="AWL2" s="6"/>
+      <c r="AWM2" s="6"/>
+      <c r="AWN2" s="6"/>
+      <c r="AWO2" s="6"/>
+      <c r="AWP2" s="6"/>
+      <c r="AWQ2" s="6"/>
+      <c r="AWR2" s="6"/>
+      <c r="AWS2" s="6"/>
+      <c r="AWT2" s="6"/>
+      <c r="AWU2" s="6"/>
+      <c r="AWV2" s="6"/>
+    </row>
+    <row r="3" spans="2:1296" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="14"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="2:1296" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="2:1296" ht="91.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="2:1296" s="4" customFormat="1" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="51"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="2:1296" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="2:1296" s="4" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="2:1296" s="4" customFormat="1" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="2:1296" s="4" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="2:1296" s="4" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="2:1296" s="4" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="2:1296" s="4" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="27"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="2:1296" s="4" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="37"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" s="4" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="35"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" s="4" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" s="4" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B20" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" s="4" customFormat="1" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="42"/>
+      <c r="K21" s="7"/>
     </row>
-    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+    <row r="22" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
     </row>
-    <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="68"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
     </row>
-    <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>32</v>
-      </c>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="68"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
     </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="68"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
     </row>
-    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="68"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
     </row>
-    <row r="7" spans="1:13" s="8" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>17</v>
-      </c>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="68"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
     </row>
-    <row r="8" spans="1:13" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="68"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
     </row>
-    <row r="9" spans="1:13" s="8" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="32"/>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="68"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
     </row>
-    <row r="10" spans="1:13" s="8" customFormat="1" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="32"/>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="68"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="68"/>
     </row>
-    <row r="11" spans="1:13" s="8" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="32"/>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="68"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
     </row>
-    <row r="12" spans="1:13" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="32"/>
-    </row>
-    <row r="13" spans="1:13" s="8" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="32"/>
-    </row>
-    <row r="14" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="32"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="32"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="32"/>
-    </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="32"/>
-    </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="32"/>
-    </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="68"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
+  <mergeCells count="13">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B9:I9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A5:H5" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>
+    <hyperlink ref="B6:I6" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageMargins left="2.1874999999999999E-2" right="8.3333333333333329E-2" top="0.21875" bottom="0.25156250000000002" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anais\Downloads\Epreuve_E5\Portfolio\t_competences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0764629B-961F-4D65-A95B-E772926F9A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5E0FE7-A133-4689-80B0-393156E5DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -163,9 +163,6 @@
     <t>▸Gérer des sauvegardes</t>
   </si>
   <si>
-    <t xml:space="preserve">▸Recenser et identifier les ressources numériques                                        ▸Mettre en place et vérifier les niveaux d’habilitation associés à un service                                                                              </t>
-  </si>
-  <si>
     <t>15/09/2025 au 13/10/2025</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
   </si>
   <si>
     <t>Projet Java - Application de modération du site R3st0.fr</t>
-  </si>
-  <si>
-    <t>Déployer un service</t>
   </si>
   <si>
     <r>
@@ -272,6 +266,15 @@
       </rPr>
       <t>https://anaisprt44.github.io/Portfolio/index.html</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">▸Gérer des sauvegardes    ▸Recenser et identifier les ressources numériques  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">▸ Déployer un service ▸Accompagner les utilisateurs dans la mise en place d’un service </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ▸Mettre en place et vérifier les niveaux d’habilitation associés à un service                                                                              </t>
   </si>
 </sst>
 </file>
@@ -904,6 +907,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -957,30 +984,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1391,28 +1394,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:1296" x14ac:dyDescent="0.25">
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="2:1296" ht="31.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="60"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="42"/>
       <c r="J2" s="9"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -2701,41 +2704,41 @@
       <c r="AWV2"/>
     </row>
     <row r="3" spans="2:1296" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="63"/>
-      <c r="I4" s="66"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="45"/>
+      <c r="I4" s="48"/>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="48"/>
+      <c r="B5" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
       <c r="G5" s="5" t="s">
         <v>29</v>
       </c>
@@ -2743,28 +2746,28 @@
         <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="2:1296" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
+      <c r="B6" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="59"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="2:1296" ht="91.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="54" t="s">
+      <c r="B7" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="32" t="s">
@@ -2788,8 +2791,8 @@
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="2:1296" s="3" customFormat="1" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="53"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="63"/>
       <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2812,14 +2815,14 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="2:1296" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="56"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="66"/>
       <c r="J9" s="9"/>
       <c r="K9" s="4"/>
     </row>
@@ -2849,7 +2852,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>24</v>
@@ -2863,7 +2866,7 @@
       <c r="J11" s="14"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="2:1296" s="3" customFormat="1" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:1296" s="3" customFormat="1" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
         <v>22</v>
       </c>
@@ -2891,9 +2894,11 @@
         <v>34</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="13"/>
+        <v>61</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
         <v>31</v>
@@ -2913,20 +2918,20 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="2:1296" s="3" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="19" t="s">
@@ -2935,7 +2940,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15" s="21"/>
       <c r="J15" s="14"/>
@@ -2943,16 +2948,16 @@
     </row>
     <row r="16" spans="2:1296" s="3" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="40" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>47</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
       <c r="G16" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H16" s="27"/>
       <c r="I16" s="25"/>
@@ -2961,10 +2966,10 @@
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>38</v>
@@ -2973,29 +2978,29 @@
       <c r="F17" s="25"/>
       <c r="G17" s="26"/>
       <c r="H17" s="27" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I17" s="25"/>
       <c r="J17" s="14"/>
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
       <c r="J18" s="14"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>23</v>
@@ -3008,7 +3013,7 @@
       <c r="G19" s="30"/>
       <c r="H19" s="30"/>
       <c r="I19" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J19" s="14" t="s">
         <v>28</v>
@@ -3016,25 +3021,25 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
       <c r="J20" s="14"/>
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="10" t="s">
@@ -3044,10 +3049,10 @@
       <c r="G21" s="31"/>
       <c r="H21" s="31"/>
       <c r="I21" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K21" s="4"/>
     </row>
@@ -3174,12 +3179,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G4:I4"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B5:F5"/>
@@ -3187,6 +3186,12 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6:I6" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>

--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anais\Downloads\Epreuve_E5\Portfolio\t_competences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5E0FE7-A133-4689-80B0-393156E5DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543B5352-C300-4092-ABA1-DA99550692A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -907,6 +907,60 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -930,60 +984,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1394,28 +1394,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:1296" x14ac:dyDescent="0.25">
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="2:1296" ht="31.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="42"/>
+      <c r="I2" s="60"/>
       <c r="J2" s="9"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -2704,41 +2704,41 @@
       <c r="AWV2"/>
     </row>
     <row r="3" spans="2:1296" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47" t="s">
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="48"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="66"/>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="48"/>
       <c r="G5" s="5" t="s">
         <v>29</v>
       </c>
@@ -2751,23 +2751,23 @@
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="2:1296" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="59"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="51"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="2:1296" ht="91.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="54" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="32" t="s">
@@ -2791,8 +2791,8 @@
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="2:1296" s="3" customFormat="1" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="61"/>
-      <c r="C8" s="63"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="55"/>
       <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2815,14 +2815,14 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="2:1296" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="64"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="66"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
       <c r="J9" s="9"/>
       <c r="K9" s="4"/>
     </row>
@@ -2896,9 +2896,7 @@
       <c r="D13" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>63</v>
-      </c>
+      <c r="E13" s="10"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
         <v>31</v>
@@ -2985,16 +2983,16 @@
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="14"/>
       <c r="K18" s="4"/>
     </row>
@@ -3021,16 +3019,16 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="53"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
       <c r="J20" s="14"/>
       <c r="K20" s="4"/>
     </row>
@@ -3179,6 +3177,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B5:F5"/>
@@ -3186,12 +3190,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6:I6" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>

--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -907,6 +907,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -960,30 +984,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1394,28 +1394,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:1296" x14ac:dyDescent="0.25">
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="2:1296" ht="31.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="60"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="9"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -2704,41 +2704,41 @@
       <c r="AWV2"/>
     </row>
     <row r="3" spans="2:1296" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65" t="s">
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="63"/>
-      <c r="I4" s="66"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="48"/>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="48"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
       <c r="G5" s="5" t="s">
         <v>29</v>
       </c>
@@ -2751,23 +2751,23 @@
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="2:1296" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="59"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="2:1296" ht="91.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="62" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="32" t="s">
@@ -2791,8 +2791,8 @@
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="2:1296" s="3" customFormat="1" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="53"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="63"/>
       <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2815,14 +2815,14 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="2:1296" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="56"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="66"/>
       <c r="J9" s="9"/>
       <c r="K9" s="4"/>
     </row>
@@ -2983,16 +2983,16 @@
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
       <c r="J18" s="14"/>
       <c r="K18" s="4"/>
     </row>
@@ -3019,16 +3019,16 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
       <c r="J20" s="14"/>
       <c r="K20" s="4"/>
     </row>
@@ -3177,12 +3177,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G4:I4"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B5:F5"/>
@@ -3190,6 +3184,12 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6:I6" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>

--- a/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
+++ b/t_competences/Tableau de synthèse - BTS SIO 2024_PORTOLLEAU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anais\Downloads\Epreuve_E5\Portfolio\t_competences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543B5352-C300-4092-ABA1-DA99550692A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B472324-BAD1-41B6-BB04-40A071C0DA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>05/01/26 au 12/02/26</t>
-  </si>
-  <si>
-    <t>▸Mettre en œuvre des outils et des stratégies de veille informationnelle</t>
   </si>
   <si>
     <t xml:space="preserve">Projet Android </t>
@@ -907,6 +904,60 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -930,60 +981,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1394,28 +1391,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:1296" x14ac:dyDescent="0.25">
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="2:1296" ht="31.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="42"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="60"/>
       <c r="J2" s="9"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -2704,41 +2701,41 @@
       <c r="AWV2"/>
     </row>
     <row r="3" spans="2:1296" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="48"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="63"/>
+      <c r="I4" s="66"/>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="2:1296" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
+      <c r="B5" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="48"/>
       <c r="G5" s="5" t="s">
         <v>29</v>
       </c>
@@ -2746,28 +2743,28 @@
         <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="2:1296" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="59"/>
+      <c r="B6" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="51"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="2:1296" ht="91.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="60" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="62" t="s">
+      <c r="B7" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="54" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="32" t="s">
@@ -2791,8 +2788,8 @@
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="2:1296" s="3" customFormat="1" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="61"/>
-      <c r="C8" s="63"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="55"/>
       <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
@@ -2815,14 +2812,14 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="2:1296" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="64"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="66"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
       <c r="J9" s="9"/>
       <c r="K9" s="4"/>
     </row>
@@ -2852,7 +2849,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>24</v>
@@ -2894,13 +2891,11 @@
         <v>34</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="17"/>
       <c r="J13" s="14"/>
@@ -2916,10 +2911,10 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="4"/>
@@ -2946,59 +2941,61 @@
     </row>
     <row r="16" spans="2:1296" s="3" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="40" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
       <c r="G16" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H16" s="27"/>
       <c r="I16" s="25"/>
       <c r="J16" s="14"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:11" s="3" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" s="3" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>38</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
+      <c r="G17" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="H17" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I17" s="25"/>
       <c r="J17" s="14"/>
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="14"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>23</v>
@@ -3019,22 +3016,22 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="53"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
       <c r="J20" s="14"/>
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" s="35" t="s">
         <v>43</v>
@@ -3046,11 +3043,9 @@
       <c r="F21" s="31"/>
       <c r="G21" s="31"/>
       <c r="H21" s="31"/>
-      <c r="I21" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="I21" s="11"/>
       <c r="J21" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K21" s="4"/>
     </row>
@@ -3177,6 +3172,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B5:F5"/>
@@ -3184,12 +3185,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6:I6" r:id="rId1" display="Adresse URL du portfolio :  https://anaisprt44.github.io/Portfolio/" xr:uid="{73D7E004-B80F-41DA-A367-A5252A13D356}"/>
